--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4593" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="605">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1779,147 +1779,120 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
+    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>Observation.component.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the component result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Observation.component.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted</t>
+  </si>
+  <si>
+    <t>predicted</t>
+  </si>
+  <si>
+    <t>Vorhersage</t>
+  </si>
+  <si>
+    <t>vorhergesagtes Messergebnis</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.id</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.code</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.value[x]</t>
+  </si>
+  <si>
     <t xml:space="preserve">type:$this}
 </t>
   </si>
   <si>
-    <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity</t>
   </si>
   <si>
     <t>valueQuantity</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
   </si>
   <si>
     <t>Observation.component.value[x].id</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
   </si>
   <si>
     <t>Observation.component.value[x].extension</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
   </si>
   <si>
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
   </si>
   <si>
     <t>Observation.component.value[x].comparator</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
   </si>
   <si>
     <t>Observation.component.value[x].unit</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
   </si>
   <si>
     <t>Observation.component.value[x].system</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
+    <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
   </si>
   <si>
     <t>Observation.component.value[x].code</t>
-  </si>
-  <si>
-    <t>Observation.component.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted</t>
-  </si>
-  <si>
-    <t>predicted</t>
-  </si>
-  <si>
-    <t>Vorhersage</t>
-  </si>
-  <si>
-    <t>vorhergesagtes Messergebnis</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.code</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component:predicted.value[x]:valueQuantity.code</t>
   </si>
   <si>
     <t>Observation.component:predicted.dataAbsentReason</t>
@@ -2245,7 +2218,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO122"/>
+  <dimension ref="A1:AO114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.09375" customWidth="true" bestFit="true"/>
@@ -13298,14 +13271,16 @@
         <v>81</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>559</v>
@@ -13326,7 +13301,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>385</v>
@@ -13340,14 +13315,12 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13365,22 +13338,22 @@
         <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>378</v>
+        <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13405,13 +13378,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13429,7 +13402,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13438,7 +13411,7 @@
         <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>103</v>
@@ -13447,35 +13420,35 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>565</v>
+        <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>385</v>
+        <v>434</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>569</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>81</v>
@@ -13487,16 +13460,20 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>106</v>
+        <v>570</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13520,13 +13497,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13544,46 +13521,46 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>108</v>
+        <v>569</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13602,18 +13579,20 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>112</v>
+        <v>573</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>113</v>
+        <v>574</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13649,19 +13628,19 @@
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>118</v>
+        <v>572</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13673,7 +13652,7 @@
         <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>81</v>
@@ -13682,7 +13661,7 @@
         <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>81</v>
@@ -13693,12 +13672,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13719,19 +13700,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>390</v>
+        <v>487</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>391</v>
+        <v>577</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>392</v>
+        <v>578</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>393</v>
+        <v>548</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>394</v>
+        <v>549</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13780,13 +13761,13 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>395</v>
+        <v>545</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
@@ -13801,7 +13782,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>396</v>
+        <v>550</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -13812,10 +13793,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13832,30 +13813,26 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>398</v>
+        <v>106</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>399</v>
+        <v>107</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>400</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q99" t="s" s="2">
-        <v>401</v>
-      </c>
+      <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
         <v>81</v>
       </c>
@@ -13875,13 +13852,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>402</v>
+        <v>81</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -13899,7 +13876,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>404</v>
+        <v>108</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13911,7 +13888,7 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>81</v>
@@ -13920,7 +13897,7 @@
         <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>81</v>
@@ -13929,46 +13906,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>577</v>
+        <v>552</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>407</v>
+        <v>112</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14016,19 +13993,19 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>411</v>
+        <v>118</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>81</v>
@@ -14037,7 +14014,7 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
@@ -14046,45 +14023,47 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>414</v>
+        <v>498</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>416</v>
+        <v>194</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14133,19 +14112,19 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>418</v>
+        <v>500</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>81</v>
@@ -14154,7 +14133,7 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>412</v>
+        <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
@@ -14163,12 +14142,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>581</v>
+        <v>554</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14176,13 +14155,13 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>81</v>
@@ -14191,19 +14170,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>421</v>
+        <v>555</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>422</v>
+        <v>556</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>423</v>
+        <v>557</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>424</v>
+        <v>261</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14228,13 +14207,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14252,10 +14231,10 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>425</v>
+        <v>554</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>91</v>
@@ -14270,13 +14249,13 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>81</v>
+        <v>558</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>412</v>
+        <v>266</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14284,10 +14263,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14307,22 +14286,22 @@
         <v>81</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>232</v>
+        <v>560</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>430</v>
+        <v>382</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14347,31 +14326,29 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14380,7 +14357,7 @@
         <v>91</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>433</v>
+        <v>81</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>103</v>
@@ -14389,35 +14366,37 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>81</v>
+        <v>564</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>434</v>
+        <v>385</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>81</v>
+        <v>386</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="B104" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>81</v>
@@ -14426,22 +14405,22 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>232</v>
+        <v>378</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>439</v>
+        <v>563</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14466,13 +14445,13 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14490,13 +14469,13 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>81</v>
@@ -14508,24 +14487,24 @@
         <v>81</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>443</v>
+        <v>564</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>444</v>
+        <v>385</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>445</v>
+        <v>386</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14536,7 +14515,7 @@
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14548,20 +14527,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>590</v>
+        <v>106</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14609,80 +14584,76 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AG105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="B106" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>487</v>
+        <v>111</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>594</v>
+        <v>112</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>595</v>
+        <v>113</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>81</v>
       </c>
@@ -14718,19 +14689,19 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>545</v>
+        <v>118</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14742,7 +14713,7 @@
         <v>81</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>81</v>
@@ -14751,7 +14722,7 @@
         <v>81</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>550</v>
+        <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>81</v>
@@ -14760,12 +14731,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14779,25 +14750,29 @@
         <v>91</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>105</v>
+        <v>390</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>106</v>
+        <v>391</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -14845,7 +14820,7 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>108</v>
+        <v>395</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14857,7 +14832,7 @@
         <v>81</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>81</v>
@@ -14866,7 +14841,7 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>81</v>
+        <v>396</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
@@ -14877,48 +14852,50 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>552</v>
+        <v>594</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>112</v>
+        <v>398</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q108" s="2"/>
+      <c r="Q108" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="R108" t="s" s="2">
         <v>81</v>
       </c>
@@ -14938,13 +14915,13 @@
         <v>81</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -14962,19 +14939,19 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>118</v>
+        <v>404</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>81</v>
@@ -14983,7 +14960,7 @@
         <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>81</v>
@@ -14992,47 +14969,45 @@
         <v>81</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>553</v>
+        <v>596</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>498</v>
+        <v>407</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>194</v>
+        <v>409</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15042,7 +15017,7 @@
         <v>81</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>81</v>
+        <v>597</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>81</v>
@@ -15081,19 +15056,19 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>500</v>
+        <v>411</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>81</v>
@@ -15102,7 +15077,7 @@
         <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>81</v>
+        <v>412</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -15111,12 +15086,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15124,13 +15099,13 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>81</v>
@@ -15139,19 +15114,17 @@
         <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>555</v>
+        <v>414</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>261</v>
+        <v>416</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15161,7 +15134,7 @@
         <v>81</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>81</v>
+        <v>417</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>81</v>
@@ -15176,13 +15149,13 @@
         <v>81</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
@@ -15200,16 +15173,16 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>554</v>
+        <v>418</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>103</v>
@@ -15218,24 +15191,24 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>558</v>
+        <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>266</v>
+        <v>412</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>600</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15249,7 +15222,7 @@
         <v>91</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>81</v>
@@ -15258,19 +15231,19 @@
         <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>560</v>
+        <v>166</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>561</v>
+        <v>421</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>562</v>
+        <v>422</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>563</v>
+        <v>423</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15280,7 +15253,7 @@
         <v>81</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>81</v>
+        <v>597</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>81</v>
@@ -15307,17 +15280,19 @@
         <v>81</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AC111" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>601</v>
+        <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>559</v>
+        <v>425</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15335,16 +15310,16 @@
         <v>81</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>565</v>
+        <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" hidden="true">
@@ -15352,11 +15327,9 @@
         <v>602</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15374,22 +15347,22 @@
         <v>81</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>378</v>
+        <v>232</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15414,13 +15387,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>81</v>
+        <v>432</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15438,7 +15411,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15447,7 +15420,7 @@
         <v>91</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>81</v>
+        <v>433</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>103</v>
@@ -15456,16 +15429,16 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>565</v>
+        <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>385</v>
+        <v>434</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>386</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" hidden="true">
@@ -15477,14 +15450,14 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15496,16 +15469,20 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>106</v>
+        <v>570</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
       </c>
@@ -15529,13 +15506,13 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>81</v>
+        <v>441</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>81</v>
+        <v>442</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15553,34 +15530,34 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>108</v>
+        <v>569</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>81</v>
+        <v>445</v>
       </c>
     </row>
     <row r="114" hidden="true">
@@ -15588,11 +15565,11 @@
         <v>604</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15611,18 +15588,20 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>112</v>
+        <v>573</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>113</v>
+        <v>574</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
       </c>
@@ -15658,19 +15637,19 @@
         <v>81</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>118</v>
+        <v>572</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15682,7 +15661,7 @@
         <v>81</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>81</v>
@@ -15691,965 +15670,17 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q116" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="R116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="P121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO122" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO122">
+  <autoFilter ref="A1:AO114">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16659,7 +15690,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI121">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-hb.xlsx
@@ -982,6 +982,14 @@
     <t>sct</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;code value="38082009"/&gt;
+  &lt;display value="Hemoglobin (substance)"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:sct.id</t>
   </si>
   <si>
@@ -997,9 +1005,6 @@
     <t>Observation.code.coding:sct.code</t>
   </si>
   <si>
-    <t>38082009</t>
-  </si>
-  <si>
     <t>Observation.code.coding:sct.display</t>
   </si>
   <si>
@@ -1012,6 +1017,13 @@
     <t>loinc</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="718-7"/&gt;
+  &lt;display value="Hemoglobin [Mass/volume] in Blood"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:loinc.id</t>
   </si>
   <si>
@@ -1025,9 +1037,6 @@
   </si>
   <si>
     <t>Observation.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>718-7</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc.display</t>
@@ -6775,7 +6784,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6846,7 +6855,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>273</v>
@@ -6961,7 +6970,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>274</v>
@@ -7078,7 +7087,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>275</v>
@@ -7197,7 +7206,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>282</v>
@@ -7314,7 +7323,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>288</v>
@@ -7360,7 +7369,7 @@
         <v>81</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>81</v>
@@ -7717,7 +7726,7 @@
         <v>81</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>81</v>
@@ -7788,7 +7797,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>273</v>
@@ -7903,7 +7912,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>274</v>
@@ -8020,7 +8029,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>275</v>
@@ -8139,7 +8148,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>282</v>
@@ -8256,7 +8265,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>288</v>
@@ -8302,7 +8311,7 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>81</v>
